--- a/Extra/TestCases_Upload_Single_File.xlsx
+++ b/Extra/TestCases_Upload_Single_File.xlsx
@@ -109,42 +109,42 @@
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Ch?c n?ng</t>
+          <t xml:space="preserve">Chức năng</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">M?c ti?u ki?m th?</t>
+          <t xml:space="preserve">Mục tiêu kiểm thử</t>
         </is>
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Ti?n ?i?u ki?n</t>
+          <t xml:space="preserve">Tiền điều kiện</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">D? li?u ki?m th?</t>
+          <t xml:space="preserve">Dữ liệu kiểm thử</t>
         </is>
       </c>
       <c r="G1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">C?c b??c th?c hi?n</t>
+          <t xml:space="preserve">Các bước thực hiện</t>
         </is>
       </c>
       <c r="H1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">K?t qu? mong ??i</t>
+          <t xml:space="preserve">Kết quả mong đợi</t>
         </is>
       </c>
       <c r="I1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Lo?i test</t>
+          <t xml:space="preserve">Loại test</t>
         </is>
       </c>
       <c r="J1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Tr?ng th?i</t>
+          <t xml:space="preserve">Trạng thái</t>
         </is>
       </c>
     </row>
@@ -161,33 +161,33 @@
       </c>
       <c r="C2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Kh?i ??ng ?ng d?ng</t>
+          <t xml:space="preserve">Khởi động ứng dụng</t>
         </is>
       </c>
       <c r="D2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra m? m?n h?nh ??ng nh?p m?c ??nh</t>
+          <t xml:space="preserve">Kiểm tra mở màn hình đăng nhập mặc định</t>
         </is>
       </c>
       <c r="E2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">?? c?i requirements, ??ng t?i th? m?c Code</t>
+          <t xml:space="preserve">Đã cài requirements, đứng tại thư mục Code</t>
         </is>
       </c>
       <c r="F2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">L?nh: python main.py ho?c python main.py login</t>
+          <t xml:space="preserve">Lệnh: python main.py hoặc python main.py login</t>
         </is>
       </c>
       <c r="G2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Ch?y l?nh kh?i ??ng.
-2. Quan s?t c?a s? hi?n th?.</t>
+          <t xml:space="preserve">1. Chạy lệnh khởi động.
+2. Quan sát cửa sổ hiển thị.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">?ng d?ng m? m?n h?nh Login, kh?ng b?o l?i kh?i ??ng.</t>
+          <t xml:space="preserve">Ứng dụng mở màn hình Login, không báo lỗi khởi động.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr" s="2">
@@ -214,17 +214,17 @@
       </c>
       <c r="C3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">??ng nh?p Admin</t>
+          <t xml:space="preserve">Đăng nhập Admin</t>
         </is>
       </c>
       <c r="D3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra admin ??ng nh?p ??ng th?ng tin</t>
+          <t xml:space="preserve">Kiểm tra admin đăng nhập đúng thông tin</t>
         </is>
       </c>
       <c r="E3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Database ?? ???c kh?i t?o t?i kho?n admin m?c ??nh</t>
+          <t xml:space="preserve">Database đã được khởi tạo tài khoản admin mặc định</t>
         </is>
       </c>
       <c r="F3" t="inlineStr" s="2">
@@ -236,15 +236,15 @@
       </c>
       <c r="G3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. M? m?n h?nh Login.
-2. Ch?n vai tr? Admin.
-3. Nh?p email, m?t kh?u.
-4. B?m ??ng nh?p.</t>
+          <t xml:space="preserve">1. Mở màn hình Login.
+2. Chọn vai trò Admin.
+3. Nhập email, mật khẩu.
+4. Bấm Đăng nhập.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">??ng nh?p th?nh c?ng v? m? Admin Panel.</t>
+          <t xml:space="preserve">Đăng nhập thành công và mở Admin Panel.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr" s="2">
@@ -271,17 +271,17 @@
       </c>
       <c r="C4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">??ng nh?p Admin</t>
+          <t xml:space="preserve">Đăng nhập Admin</t>
         </is>
       </c>
       <c r="D4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra b?o l?i khi sai m?t kh?u</t>
+          <t xml:space="preserve">Kiểm tra báo lỗi khi sai mật khẩu</t>
         </is>
       </c>
       <c r="E4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">C? t?i kho?n admin m?c ??nh</t>
+          <t xml:space="preserve">Có tài khoản admin mặc định</t>
         </is>
       </c>
       <c r="F4" t="inlineStr" s="2">
@@ -293,14 +293,14 @@
       </c>
       <c r="G4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Ch?n vai tr? Admin.
-2. Nh?p email ??ng, m?t kh?u sai.
-3. B?m ??ng nh?p.</t>
+          <t xml:space="preserve">1. Chọn vai trò Admin.
+2. Nhập email đúng, mật khẩu sai.
+3. Bấm Đăng nhập.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hi?n th? th?ng b?o m?t kh?u kh?ng ??ng, kh?ng chuy?n m?n h?nh.</t>
+          <t xml:space="preserve">Hiển thị thông báo mật khẩu không đúng, không chuyển màn hình.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr" s="2">
@@ -327,36 +327,36 @@
       </c>
       <c r="C5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ph?n quy?n ??ng nh?p</t>
+          <t xml:space="preserve">Phân quyền đăng nhập</t>
         </is>
       </c>
       <c r="D5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra user kh?ng ??ng nh?p ???c v?o vai tr? Admin</t>
+          <t xml:space="preserve">Kiểm tra user không đăng nhập được vào vai trò Admin</t>
         </is>
       </c>
       <c r="E5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">?? c? m?t t?i kho?n user h?p l?</t>
+          <t xml:space="preserve">Đã có một tài khoản user hợp lệ</t>
         </is>
       </c>
       <c r="F5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email user th??ng
-Password ??ng
+          <t xml:space="preserve">Email user thường
+Password đúng
 Role: Admin</t>
         </is>
       </c>
       <c r="G5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Ch?n vai tr? Admin.
-2. Nh?p th?ng tin t?i kho?n user.
-3. B?m ??ng nh?p.</t>
+          <t xml:space="preserve">1. Chọn vai trò Admin.
+2. Nhập thông tin tài khoản user.
+3. Bấm Đăng nhập.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hi?n th? th?ng b?o t?i kho?n kh?ng ??ng vai tr? ?? ch?n.</t>
+          <t xml:space="preserve">Hiển thị thông báo tài khoản không đúng vai trò đã chọn.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr" s="2">
@@ -383,36 +383,36 @@
       </c>
       <c r="C6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">??ng k? t?i kho?n</t>
+          <t xml:space="preserve">Đăng ký tài khoản</t>
         </is>
       </c>
       <c r="D6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra ??ng k? user h?p l?</t>
+          <t xml:space="preserve">Kiểm tra đăng ký user hợp lệ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email test ch?a t?n t?i trong database</t>
+          <t xml:space="preserve">Email test chưa tồn tại trong database</t>
         </is>
       </c>
       <c r="F6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">H? t?n: Nguy?n V?n A
+          <t xml:space="preserve">Họ tên: Nguyễn Văn A
 Email: user01@test.local
 Password: 1234</t>
         </is>
       </c>
       <c r="G6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. M? m?n h?nh ??ng k?.
-2. Nh?p ??y ?? th?ng tin h?p l?.
-3. B?m ??ng k?.</t>
+          <t xml:space="preserve">1. Mở màn hình Đăng ký.
+2. Nhập đầy đủ thông tin hợp lệ.
+3. Bấm Đăng ký.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">T?i kho?n ???c t?o v?i role user, c? th? d?ng ?? ??ng nh?p.</t>
+          <t xml:space="preserve">Tài khoản được tạo với role user, có thể dùng để đăng nhập.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr" s="2">
@@ -439,35 +439,35 @@
       </c>
       <c r="C7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">??ng k? t?i kho?n</t>
+          <t xml:space="preserve">Đăng ký tài khoản</t>
         </is>
       </c>
       <c r="D7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra validate email kh?ng h?p l?</t>
+          <t xml:space="preserve">Kiểm tra validate email không hợp lệ</t>
         </is>
       </c>
       <c r="E7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">?ng d?ng ?ang ? m?n h?nh ??ng k?</t>
+          <t xml:space="preserve">Ứng dụng đang ở màn hình Đăng ký</t>
         </is>
       </c>
       <c r="F7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">H? t?n: Test User
+          <t xml:space="preserve">Họ tên: Test User
 Email: user01test.local
 Password: 1234</t>
         </is>
       </c>
       <c r="G7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Nh?p email kh?ng c? k? t? @.
-2. B?m ??ng k?.</t>
+          <t xml:space="preserve">1. Nhập email không có ký tự @.
+2. Bấm Đăng ký.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hi?n th? th?ng b?o Email kh?ng h?p l?, kh?ng t?o t?i kho?n.</t>
+          <t xml:space="preserve">Hiển thị thông báo Email không hợp lệ, không tạo tài khoản.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr" s="2">
@@ -494,36 +494,36 @@
       </c>
       <c r="C8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">??ng k? t?i kho?n</t>
+          <t xml:space="preserve">Đăng ký tài khoản</t>
         </is>
       </c>
       <c r="D8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra kh?ng cho ??ng k? email tr?ng</t>
+          <t xml:space="preserve">Kiểm tra không cho đăng ký email trùng</t>
         </is>
       </c>
       <c r="E8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Email user01@test.local ?? t?n t?i</t>
+          <t xml:space="preserve">Email user01@test.local đã tồn tại</t>
         </is>
       </c>
       <c r="F8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">H? t?n: Nguy?n V?n B
+          <t xml:space="preserve">Họ tên: Nguyễn Văn B
 Email: user01@test.local
 Password: 1234</t>
         </is>
       </c>
       <c r="G8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. M? ??ng k?.
-2. Nh?p email ?? t?n t?i.
-3. B?m ??ng k?.</t>
+          <t xml:space="preserve">1. Mở Đăng ký.
+2. Nhập email đã tồn tại.
+3. Bấm Đăng ký.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hi?n th? th?ng b?o email ?? t?n t?i, database kh?ng th?m b?n ghi m?i.</t>
+          <t xml:space="preserve">Hiển thị thông báo email đã tồn tại, database không thêm bản ghi mới.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr" s="2">
@@ -550,17 +550,17 @@
       </c>
       <c r="C9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">??ng nh?p User</t>
+          <t xml:space="preserve">Đăng nhập User</t>
         </is>
       </c>
       <c r="D9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra user ??ng nh?p ??ng th?ng tin</t>
+          <t xml:space="preserve">Kiểm tra user đăng nhập đúng thông tin</t>
         </is>
       </c>
       <c r="E9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">?? c? t?i kho?n user active</t>
+          <t xml:space="preserve">Đã có tài khoản user active</t>
         </is>
       </c>
       <c r="F9" t="inlineStr" s="2">
@@ -572,15 +572,15 @@
       </c>
       <c r="G9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. M? Login.
-2. Ch?n vai tr? User.
-3. Nh?p email, m?t kh?u.
-4. B?m ??ng nh?p.</t>
+          <t xml:space="preserve">1. Mở Login.
+2. Chọn vai trò User.
+3. Nhập email, mật khẩu.
+4. Bấm Đăng nhập.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">??ng nh?p th?nh c?ng v? m? giao di?n Client/Upload Files.</t>
+          <t xml:space="preserve">Đăng nhập thành công và mở giao diện Client/Upload Files.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr" s="2">
@@ -607,17 +607,17 @@
       </c>
       <c r="C10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra k?t n?i server</t>
+          <t xml:space="preserve">Kiểm tra kết nối server</t>
         </is>
       </c>
       <c r="D10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra client b?o ch?a k?t n?i khi server t?t</t>
+          <t xml:space="preserve">Kiểm tra client báo chưa kết nối khi server tắt</t>
         </is>
       </c>
       <c r="E10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ch?a b?t server ho?c port 8888 ch?a listen</t>
+          <t xml:space="preserve">Chưa bật server hoặc port 8888 chưa listen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr" s="2">
@@ -628,13 +628,13 @@
       </c>
       <c r="G10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. M? Client.
-2. B?m Ki?m tra tr?ng th?i server.</t>
+          <t xml:space="preserve">1. Mở Client.
+2. Bấm Kiểm tra trạng thái server.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Nh?n tr?ng th?i hi?n th? Server: Ch?a k?t n?i 127.0.0.1:8888.</t>
+          <t xml:space="preserve">Nhãn trạng thái hiển thị Server: Chưa kết nối 127.0.0.1:8888.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr" s="2">
@@ -661,17 +661,17 @@
       </c>
       <c r="C11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">B?t Server</t>
+          <t xml:space="preserve">Bật Server</t>
         </is>
       </c>
       <c r="D11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra b?t server t? Admin/Server Monitor</t>
+          <t xml:space="preserve">Kiểm tra bật server từ Admin/Server Monitor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Admin ?? ??ng nh?p ho?c m? python main.py server</t>
+          <t xml:space="preserve">Admin đã đăng nhập hoặc mở python main.py server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr" s="2">
@@ -682,14 +682,14 @@
       </c>
       <c r="G11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. V?o tab Server ho?c c?a s? Upload Server.
-2. B?m B?t ??u.
-3. Qua Client b?m Ki?m tra.</t>
+          <t xml:space="preserve">1. Vào tab Server hoặc cửa sổ Upload Server.
+2. Bấm Bắt đầu.
+3. Qua Client bấm Kiểm tra.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Server b?t ??u l?ng nghe, Client b?o ?? k?t n?i 127.0.0.1:8888.</t>
+          <t xml:space="preserve">Server bắt đầu lắng nghe, Client báo Đã kết nối 127.0.0.1:8888.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr" s="2">
@@ -716,34 +716,34 @@
       </c>
       <c r="C12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ch?n file upload</t>
+          <t xml:space="preserve">Chọn file upload</t>
         </is>
       </c>
       <c r="D12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra ch?n file h?p l? b?ng Browse</t>
+          <t xml:space="preserve">Kiểm tra chọn file hợp lệ bằng Browse</t>
         </is>
       </c>
       <c r="E12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Client ?? ??ng nh?p, server c? th? ch?a c?n b?t</t>
+          <t xml:space="preserve">Client đã đăng nhập, server có thể chưa cần bật</t>
         </is>
       </c>
       <c r="F12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File: Extra/test-files/B?O C?O ?? XU?T D? ?N.docx</t>
+          <t xml:space="preserve">File: Extra/test-files/BÁO CÁO ĐỀ XUẤT DỰ ÁN.docx</t>
         </is>
       </c>
       <c r="G12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. V?o Upload file.
-2. B?m Ch?n file.
-3. Ch?n m?t file h?p l?.</t>
+          <t xml:space="preserve">1. Vào Upload file.
+2. Bấm Chọn file.
+3. Chọn một file hợp lệ.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">T?n file v? dung l??ng hi?n th? ??ng, n?t Start ???c b?t, progress v? 0%.</t>
+          <t xml:space="preserve">Tên file và dung lượng hiển thị đúng, nút Start được bật, progress về 0%.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr" s="2">
@@ -770,33 +770,33 @@
       </c>
       <c r="C13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">K?o th? file</t>
+          <t xml:space="preserve">Kéo thả file</t>
         </is>
       </c>
       <c r="D13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra k?o th? th? m?c b? t? ch?i</t>
+          <t xml:space="preserve">Kiểm tra kéo thả thư mục bị từ chối</t>
         </is>
       </c>
       <c r="E13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Client ?ang ? tr?ng th?i stopped</t>
+          <t xml:space="preserve">Client đang ở trạng thái stopped</t>
         </is>
       </c>
       <c r="F13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">M?t th? m?c b?t k? tr?n m?y</t>
+          <t xml:space="preserve">Một thư mục bất kỳ trên máy</t>
         </is>
       </c>
       <c r="G13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. K?o th? m?c v?o v?ng upload.
-2. Quan s?t th?ng b?o.</t>
+          <t xml:space="preserve">1. Kéo thư mục vào vùng upload.
+2. Quan sát thông báo.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">?ng d?ng c?nh b?o ch? h? tr? k?o th? m?t file, kh?ng nh?n th? m?c.</t>
+          <t xml:space="preserve">Ứng dụng cảnh báo chỉ hỗ trợ kéo thả một file, không nhận thư mục.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr" s="2">
@@ -828,28 +828,28 @@
       </c>
       <c r="D14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra kh?ng cho Start khi ch?a ch?n file</t>
+          <t xml:space="preserve">Kiểm tra không cho Start khi chưa chọn file</t>
         </is>
       </c>
       <c r="E14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Client ?ang m?, ch?a ch?n file</t>
+          <t xml:space="preserve">Client đang mở, chưa chọn file</t>
         </is>
       </c>
       <c r="F14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Kh?ng c?</t>
+          <t xml:space="preserve">Không có</t>
         </is>
       </c>
       <c r="G14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Kh?ng ch?n file.
-2. B?m Start n?u n?t c? th? b?m ho?c g?i thao t?c start.</t>
+          <t xml:space="preserve">1. Không chọn file.
+2. Bấm Start nếu nút có thể bấm hoặc gọi thao tác start.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Hi?n th? c?nh b?o B?n ch?a ch?n file ?? upload, kh?ng t?o k?t n?i upload.</t>
+          <t xml:space="preserve">Hiển thị cảnh báo Bạn chưa chọn file để upload, không tạo kết nối upload.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr" s="2">
@@ -881,31 +881,31 @@
       </c>
       <c r="D15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra upload file nh? th?nh c?ng</t>
+          <t xml:space="preserve">Kiểm tra upload file nhỏ thành công</t>
         </is>
       </c>
       <c r="E15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Server ?? b?t, Client ?? ch?n file h?p l?</t>
+          <t xml:space="preserve">Server đã bật, Client đã chọn file hợp lệ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File nh? d??i 5 MB
-Policy: B? qua n?u file ?? c?
+          <t xml:space="preserve">File nhỏ dưới 5 MB
+Policy: Bỏ qua nếu file đã có
 Speed: 5 MB/s</t>
         </is>
       </c>
       <c r="G15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Ch?n file nh?.
-2. B?m Start.
-3. Ch? progress ho?n t?t.</t>
+          <t xml:space="preserve">1. Chọn file nhỏ.
+2. Bấm Start.
+3. Chờ progress hoàn tất.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Progress ??t 100%, th?ng b?o upload th?nh c?ng, checksum kh?p, l?ch s? ghi Verified.</t>
+          <t xml:space="preserve">Progress đạt 100%, thông báo upload thành công, checksum khớp, lịch sử ghi Verified.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr" s="2">
@@ -937,30 +937,30 @@
       </c>
       <c r="D16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra t?m d?ng khi ?ang upload file l?n</t>
+          <t xml:space="preserve">Kiểm tra tạm dừng khi đang upload file lớn</t>
         </is>
       </c>
       <c r="E16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Server ?? b?t, ?ang upload file ?? l?n ?? quan s?t</t>
+          <t xml:space="preserve">Server đã bật, đang upload file đủ lớn để quan sát</t>
         </is>
       </c>
       <c r="F16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File l?n kho?ng 20 MB tr? l?n
+          <t xml:space="preserve">File lớn khoảng 20 MB trở lên
 Speed: 2 MB/s</t>
         </is>
       </c>
       <c r="G16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Ch?n file l?n.
-2. B?m Start.
-3. Khi ?ang ch?y b?m Pause.</t>
+          <t xml:space="preserve">1. Chọn file lớn.
+2. Bấm Start.
+3. Khi đang chạy bấm Pause.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Tr?ng th?i chuy?n ?? t?m d?ng, progress kh?ng t?ng ti?p, n?t Resume v? Stop ???c b?t.</t>
+          <t xml:space="preserve">Trạng thái chuyển Đã tạm dừng, progress không tăng tiếp, nút Resume và Stop được bật.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr" s="2">
@@ -992,28 +992,28 @@
       </c>
       <c r="D17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra ti?p t?c upload sau khi Pause</t>
+          <t xml:space="preserve">Kiểm tra tiếp tục upload sau khi Pause</t>
         </is>
       </c>
       <c r="E17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Upload ?ang ? tr?ng th?i paused t? TC015</t>
+          <t xml:space="preserve">Upload đang ở trạng thái paused từ TC015</t>
         </is>
       </c>
       <c r="F17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File ?ang upload d?</t>
+          <t xml:space="preserve">File đang upload dở</t>
         </is>
       </c>
       <c r="G17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. B?m Resume.
-2. Theo d?i progress ??n khi ho?n t?t.</t>
+          <t xml:space="preserve">1. Bấm Resume.
+2. Theo dõi progress đến khi hoàn tất.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Upload ti?p t?c t? v? tr? ?ang d?ng, progress t?ng l?i v? k?t th?c Verified.</t>
+          <t xml:space="preserve">Upload tiếp tục từ vị trí đang dừng, progress tăng lại và kết thúc Verified.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr" s="2">
@@ -1045,29 +1045,29 @@
       </c>
       <c r="D18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra d?ng upload gi?a ch?ng</t>
+          <t xml:space="preserve">Kiểm tra dừng upload giữa chừng</t>
         </is>
       </c>
       <c r="E18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Server ?? b?t, ?ang upload file l?n</t>
+          <t xml:space="preserve">Server đã bật, đang upload file lớn</t>
         </is>
       </c>
       <c r="F18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File l?n
+          <t xml:space="preserve">File lớn
 Speed: 2 MB/s</t>
         </is>
       </c>
       <c r="G18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. B?m Start upload file l?n.
-2. B?m Stop khi progress ch?a ??t 100%.</t>
+          <t xml:space="preserve">1. Bấm Start upload file lớn.
+2. Bấm Stop khi progress chưa đạt 100%.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Upload d?ng, socket ??ng, tr?ng th?i ?? d?ng, l?ch s? ghi Stopped, c? th? ch?n/start l?i file.</t>
+          <t xml:space="preserve">Upload dừng, socket đóng, trạng thái Đã dừng, lịch sử ghi Stopped, có thể chọn/start lại file.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr" s="2">
@@ -1094,39 +1094,40 @@
       </c>
       <c r="C19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File tr?ng - Skip</t>
+          <t xml:space="preserve">Mất kết nối khi upload</t>
         </is>
       </c>
       <c r="D19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra ch?nh s?ch b? qua n?u file ?? c?</t>
+          <t xml:space="preserve">Kiểm tra ứng dụng xử lý khi server bị tắt giữa quá trình upload</t>
         </is>
       </c>
       <c r="E19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Server ?? c? s?n file c?ng t?n v? c?ng checksum</t>
+          <t xml:space="preserve">Server đang bật, Client đang upload file lớn</t>
         </is>
       </c>
       <c r="F19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Policy: B? qua n?u file ?? c?</t>
+          <t xml:space="preserve">File lớn khoảng 20 MB trở lên
+Speed: 2 MB/s</t>
         </is>
       </c>
       <c r="G19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Ch?n l?i ??ng file ?? upload th?nh c?ng.
-2. Ch?n policy B? qua n?u file ?? c?.
-3. B?m Start.</t>
+          <t xml:space="preserve">1. Chọn file lớn và bấm Start.
+2. Khi progress đang chạy, tắt Server hoặc bấm dừng server.
+3. Quan sát thông báo trên Client.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Client nh?n tr?ng th?i Skipped, kh?ng t?o th?m b?n sao file tr?n server.</t>
+          <t xml:space="preserve">Client hiển thị upload thất bại hoặc mất kết nối, trạng thái dừng lại, lịch sử ghi Failed nếu có.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Functional</t>
+          <t xml:space="preserve">Negative</t>
         </is>
       </c>
       <c r="J19" t="inlineStr" s="2">
@@ -1148,35 +1149,35 @@
       </c>
       <c r="C20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File tr?ng - Overwrite</t>
+          <t xml:space="preserve">Lịch sử upload</t>
         </is>
       </c>
       <c r="D20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra ch?nh s?ch ghi ?? file c?</t>
+          <t xml:space="preserve">Kiểm tra màn hình My Uploads hiển thị lịch sử sau khi upload</t>
         </is>
       </c>
       <c r="E20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Server ?? c? file c?ng t?n</t>
+          <t xml:space="preserve">Đã có ít nhất một lần upload thành công hoặc thất bại</t>
         </is>
       </c>
       <c r="F20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File c?ng t?n nh?ng n?i dung m?i
-Policy: Ghi ?? file c?</t>
+          <t xml:space="preserve">Tài khoản user đang đăng nhập
+File vừa upload</t>
         </is>
       </c>
       <c r="G20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Ch?n file c?ng t?n.
-2. Ch?n policy Ghi ?? file c?.
-3. B?m Start.</t>
+          <t xml:space="preserve">1. Upload một file bất kỳ.
+2. Chuyển sang tab My Uploads.
+3. Kiểm tra thông tin dòng lịch sử.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Upload th?nh c?ng, file tr?n server ???c c?p nh?t n?i dung m?i, l?ch s? ghi Verified.</t>
+          <t xml:space="preserve">My Uploads hiển thị tên file, dung lượng, server, trạng thái và thời gian upload đúng với lần vừa thực hiện.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr" s="2">
@@ -1203,34 +1204,36 @@
       </c>
       <c r="C21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">File tr?ng - Auto rename</t>
+          <t xml:space="preserve">Giới hạn tốc độ upload</t>
         </is>
       </c>
       <c r="D21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra ch?nh s?ch ??i t?n t? ??ng</t>
+          <t xml:space="preserve">Kiểm tra lựa chọn tốc độ demo ảnh hưởng đến tốc độ upload hiển thị</t>
         </is>
       </c>
       <c r="E21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Server ?? c? file c?ng t?n</t>
+          <t xml:space="preserve">Server đã bật, Client đã chọn file đủ lớn để quan sát tốc độ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Policy: ??i t?n t? ??ng</t>
+          <t xml:space="preserve">File lớn khoảng 20 MB trở lên
+Speed: 2 MB/s hoặc 5 MB/s</t>
         </is>
       </c>
       <c r="G21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. Ch?n file tr?ng t?n.
-2. Ch?n policy ??i t?n t? ??ng.
-3. B?m Start.</t>
+          <t xml:space="preserve">1. Chọn file lớn.
+2. Chọn tốc độ demo 2 MB/s.
+3. Bấm Start và quan sát tốc độ hiển thị.
+4. Lặp lại với 5 MB/s nếu cần so sánh.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Server l?u th?nh file t?n m?i kh?ng tr?ng, upload Verified, file c? v?n c?n.</t>
+          <t xml:space="preserve">Tốc độ upload hiển thị gần với mức đã chọn, progress tăng ổn định và upload hoàn tất thành công.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr" s="2">
@@ -1257,36 +1260,36 @@
       </c>
       <c r="C22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Admin ki?m tra d? li?u</t>
+          <t xml:space="preserve">Admin kiểm tra dữ liệu</t>
         </is>
       </c>
       <c r="D22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Ki?m tra Admin xem file/l?ch s? sau upload</t>
+          <t xml:space="preserve">Kiểm tra Admin xem file/lịch sử sau upload</t>
         </is>
       </c>
       <c r="E22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">?? c? ?t nh?t m?t l??t upload th?nh c?ng t? user</t>
+          <t xml:space="preserve">Đã có ít nhất một lượt upload thành công từ user</t>
         </is>
       </c>
       <c r="F22" t="inlineStr" s="2">
         <is>
           <t xml:space="preserve">Admin account
-File v?a upload</t>
+File vừa upload</t>
         </is>
       </c>
       <c r="G22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">1. ??ng nh?p Admin.
-2. M? tab Files ki?m tra file.
-3. M? tab Users xem user.
-4. M? tab Analytics/Security n?u c?.</t>
+          <t xml:space="preserve">1. Đăng nhập Admin.
+2. Mở tab Files kiểm tra file.
+3. Mở tab Users xem user.
+4. Mở tab Analytics/Security nếu có.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr" s="2">
         <is>
-          <t xml:space="preserve">Admin th?y file ?? nh?n, ng??i upload/l?ch s? hi?n th? ??ng, th?ng k? ???c c?p nh?t.</t>
+          <t xml:space="preserve">Admin thấy file đã nhận, người upload/lịch sử hiển thị đúng, thống kê được cập nhật.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr" s="2">
